--- a/Allas tips excel/Anneli_VM_Tips_2026.xlsx
+++ b/Allas tips excel/Anneli_VM_Tips_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VM2026\Allas tips excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39D481AE-0525-412F-A86D-E67EB3C776CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7556597-2248-458C-93E6-906BCD7A280C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1065" windowWidth="25455" windowHeight="15135" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3435" yWindow="2160" windowWidth="22635" windowHeight="12855" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instruktion" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6112" uniqueCount="933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6076" uniqueCount="933">
   <si>
     <t>Fält</t>
   </si>
@@ -4332,15 +4332,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="58" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="58" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="58" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4361,6 +4352,15 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="57" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="58" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="58" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="58" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4793,10 +4793,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -5395,168 +5391,204 @@
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>24</v>
+      <c r="B8" s="2" t="str">
+        <f>'1. Gruppspel'!B62</f>
+        <v>Mexiko</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <f>'1. Gruppspel'!C62</f>
+        <v>Sydkorea</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <f>'1. Gruppspel'!D62</f>
+        <v>Tjeckien</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>35</v>
+      <c r="B9" s="2" t="str">
+        <f>'1. Gruppspel'!B63</f>
+        <v>Schweiz</v>
+      </c>
+      <c r="C9" s="2" t="str">
+        <f>'1. Gruppspel'!C63</f>
+        <v>Kanada</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <f>'1. Gruppspel'!D63</f>
+        <v>Bosnien och Hercegovina</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>50</v>
+      <c r="B10" s="2" t="str">
+        <f>'1. Gruppspel'!B64</f>
+        <v>Brasilien</v>
+      </c>
+      <c r="C10" s="2" t="str">
+        <f>'1. Gruppspel'!C64</f>
+        <v>Marocko</v>
+      </c>
+      <c r="D10" s="2" t="str">
+        <f>'1. Gruppspel'!D64</f>
+        <v>Skottland</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>59</v>
+      <c r="B11" s="2" t="str">
+        <f>'1. Gruppspel'!B65</f>
+        <v>USA</v>
+      </c>
+      <c r="C11" s="2" t="str">
+        <f>'1. Gruppspel'!C65</f>
+        <v>Turkiet</v>
+      </c>
+      <c r="D11" s="2" t="str">
+        <f>'1. Gruppspel'!D65</f>
+        <v>Paraguay</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>65</v>
+      <c r="B12" s="2" t="str">
+        <f>'1. Gruppspel'!B66</f>
+        <v>Tyskland</v>
+      </c>
+      <c r="C12" s="2" t="str">
+        <f>'1. Gruppspel'!C66</f>
+        <v>Ecuador</v>
+      </c>
+      <c r="D12" s="2" t="str">
+        <f>'1. Gruppspel'!D66</f>
+        <v>Elfenbenskusten</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>73</v>
+      <c r="B13" s="2" t="str">
+        <f>'1. Gruppspel'!B67</f>
+        <v>Nederländerna</v>
+      </c>
+      <c r="C13" s="2" t="str">
+        <f>'1. Gruppspel'!C67</f>
+        <v>Japan</v>
+      </c>
+      <c r="D13" s="2" t="str">
+        <f>'1. Gruppspel'!D67</f>
+        <v>Sverige</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>83</v>
+      <c r="B14" s="2" t="str">
+        <f>'1. Gruppspel'!B68</f>
+        <v>Belgien</v>
+      </c>
+      <c r="C14" s="2" t="str">
+        <f>'1. Gruppspel'!C68</f>
+        <v>Iran</v>
+      </c>
+      <c r="D14" s="2" t="str">
+        <f>'1. Gruppspel'!D68</f>
+        <v>Egypten</v>
       </c>
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>93</v>
+      <c r="B15" s="2" t="str">
+        <f>'1. Gruppspel'!B69</f>
+        <v>Spanien</v>
+      </c>
+      <c r="C15" s="2" t="str">
+        <f>'1. Gruppspel'!C69</f>
+        <v>Uruguay</v>
+      </c>
+      <c r="D15" s="2" t="str">
+        <f>'1. Gruppspel'!D69</f>
+        <v>Saudiarabien</v>
       </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>99</v>
+      <c r="B16" s="2" t="str">
+        <f>'1. Gruppspel'!B70</f>
+        <v>Frankrike</v>
+      </c>
+      <c r="C16" s="2" t="str">
+        <f>'1. Gruppspel'!C70</f>
+        <v>Norge</v>
+      </c>
+      <c r="D16" s="2" t="str">
+        <f>'1. Gruppspel'!D70</f>
+        <v>Senegal</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>102</v>
+      <c r="B17" s="2" t="str">
+        <f>'1. Gruppspel'!B71</f>
+        <v>Argentina</v>
+      </c>
+      <c r="C17" s="2" t="str">
+        <f>'1. Gruppspel'!C71</f>
+        <v>Österrike</v>
+      </c>
+      <c r="D17" s="2" t="str">
+        <f>'1. Gruppspel'!D71</f>
+        <v>Algeriet</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>112</v>
+      <c r="B18" s="2" t="str">
+        <f>'1. Gruppspel'!B72</f>
+        <v>Portugal</v>
+      </c>
+      <c r="C18" s="2" t="str">
+        <f>'1. Gruppspel'!C72</f>
+        <v>Colombia</v>
+      </c>
+      <c r="D18" s="2" t="str">
+        <f>'1. Gruppspel'!D72</f>
+        <v>DR Kongo</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>124</v>
+      <c r="B19" s="2" t="str">
+        <f>'1. Gruppspel'!B73</f>
+        <v>England</v>
+      </c>
+      <c r="C19" s="2" t="str">
+        <f>'1. Gruppspel'!C73</f>
+        <v>Kroatien</v>
+      </c>
+      <c r="D19" s="2" t="str">
+        <f>'1. Gruppspel'!D73</f>
+        <v>Ghana</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -7126,13 +7158,13 @@
     </row>
     <row r="3" spans="2:35" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="127"/>
-      <c r="O3" s="211" t="s">
+      <c r="O3" s="208" t="s">
         <v>353</v>
       </c>
-      <c r="P3" s="212"/>
-      <c r="Q3" s="212"/>
-      <c r="R3" s="212"/>
-      <c r="S3" s="213"/>
+      <c r="P3" s="209"/>
+      <c r="Q3" s="209"/>
+      <c r="R3" s="209"/>
+      <c r="S3" s="210"/>
       <c r="AF3" s="128"/>
     </row>
     <row r="4" spans="2:35" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
@@ -7142,11 +7174,11 @@
       </c>
       <c r="D4" s="205"/>
       <c r="E4" s="205"/>
-      <c r="O4" s="214"/>
-      <c r="P4" s="215"/>
-      <c r="Q4" s="215"/>
-      <c r="R4" s="215"/>
-      <c r="S4" s="216"/>
+      <c r="O4" s="211"/>
+      <c r="P4" s="212"/>
+      <c r="Q4" s="212"/>
+      <c r="R4" s="212"/>
+      <c r="S4" s="213"/>
       <c r="AC4" s="205" t="s">
         <v>914</v>
       </c>
@@ -7192,7 +7224,7 @@
     </row>
     <row r="6" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="127"/>
-      <c r="C6" s="210" t="s">
+      <c r="C6" s="207" t="s">
         <v>251</v>
       </c>
       <c r="D6" s="115" t="str">
@@ -7236,7 +7268,7 @@
     </row>
     <row r="7" spans="2:35" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="127"/>
-      <c r="C7" s="210"/>
+      <c r="C7" s="207"/>
       <c r="E7" s="114"/>
       <c r="F7" s="205" t="s">
         <v>913</v>
@@ -7274,7 +7306,7 @@
     </row>
     <row r="8" spans="2:35" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="127"/>
-      <c r="C8" s="210"/>
+      <c r="C8" s="207"/>
       <c r="D8" s="122" t="str">
         <f>INDEX(_Listor!$BY$3:$BZ$18,MATCH("M74",_Listor!$BX$3:$BX$18,0),2)</f>
         <v>Paraguay</v>
@@ -7982,11 +8014,11 @@
       <c r="M26" s="205"/>
       <c r="N26" s="205"/>
       <c r="O26" s="114"/>
-      <c r="P26" s="207" t="s">
+      <c r="P26" s="214" t="s">
         <v>922</v>
       </c>
-      <c r="Q26" s="208"/>
-      <c r="R26" s="209"/>
+      <c r="Q26" s="215"/>
+      <c r="R26" s="216"/>
       <c r="S26" s="114"/>
       <c r="T26" s="205" t="s">
         <v>916</v>
@@ -9031,17 +9063,21 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="O3:S4"/>
-    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="P34:R34"/>
+    <mergeCell ref="T26:V26"/>
+    <mergeCell ref="L28:L30"/>
+    <mergeCell ref="I41:I43"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="W13:Y13"/>
+    <mergeCell ref="Y41:Y43"/>
+    <mergeCell ref="Y15:Y17"/>
+    <mergeCell ref="V28:V30"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C24:C26"/>
     <mergeCell ref="F35:F37"/>
     <mergeCell ref="AE50:AE52"/>
     <mergeCell ref="AE44:AE46"/>
@@ -9058,21 +9094,17 @@
     <mergeCell ref="AE32:AE34"/>
     <mergeCell ref="AE24:AE26"/>
     <mergeCell ref="P26:R26"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="W13:Y13"/>
-    <mergeCell ref="Y41:Y43"/>
-    <mergeCell ref="Y15:Y17"/>
-    <mergeCell ref="V28:V30"/>
-    <mergeCell ref="P34:R34"/>
-    <mergeCell ref="T26:V26"/>
-    <mergeCell ref="L28:L30"/>
-    <mergeCell ref="I41:I43"/>
-    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="O3:S4"/>
+    <mergeCell ref="F21:F23"/>
   </mergeCells>
   <conditionalFormatting sqref="P26:R26">
     <cfRule type="expression" dxfId="0" priority="1">
